--- a/results/Int All Data -0.2/Rando_9_permute.xlsx
+++ b/results/Int All Data -0.2/Rando_9_permute.xlsx
@@ -440,37 +440,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7836012861736334</v>
+        <v>0.790032154340836</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>accy_kurtosis</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7836012861736334</v>
+        <v>0.790032154340836</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>accy_energy</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7845659163987139</v>
+        <v>0.7897106109324759</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7871435176428556</v>
+        <v>0.790032154340836</v>
       </c>
     </row>
     <row r="6">
@@ -480,67 +480,67 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7884612151398609</v>
+        <v>0.7955666939873485</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>accz_perm_entropy</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7865372086669609</v>
+        <v>0.7877340646869679</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>accz_svd_entropy</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.7884507071853393</v>
+        <v>0.79005842422714</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.7865056848033962</v>
+        <v>0.7933106361515667</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.7865056848033962</v>
+        <v>0.7946651114893974</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>accy_skewness</t>
+          <t>accy_rms</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.7852090032154342</v>
+        <v>0.7962413046676333</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>accz_skewness</t>
+          <t>accz_ptp</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.7845606624214531</v>
+        <v>0.7917974907004602</v>
       </c>
     </row>
     <row r="13">
@@ -550,507 +550,507 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.7842706428766577</v>
+        <v>0.7947123972847445</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>accz_mean</t>
+          <t>accz_peaks</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.7724260765399407</v>
+        <v>0.7956822814870856</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.7720782632452767</v>
+        <v>0.7950286867158438</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>accz_max</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.7551940819200134</v>
+        <v>0.795350230124204</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.7538921463547905</v>
+        <v>0.7956770275098249</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>accz_ptp</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.7500809112498161</v>
+        <v>0.7947229052392661</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.7500756572725553</v>
+        <v>0.7950444486476262</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>accy_entropy</t>
+          <t>accx_mean</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.7507187440892755</v>
+        <v>0.7982493747767059</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>accx_svd_entropy</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.7513986087468214</v>
+        <v>0.7995250404556249</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.7449152008070109</v>
+        <v>0.7995302944328857</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.7545404871487715</v>
+        <v>0.7995302944328857</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>accy_std</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.7617510455414749</v>
+        <v>0.8027614904482694</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.7617510455414749</v>
+        <v>0.7995250404556249</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>accx_pct_5</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.7617510455414749</v>
+        <v>0.8177321732551541</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>accy_peaks</t>
+          <t>accx_min</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.7692621314334951</v>
+        <v>0.8217861421095769</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.7705745749532396</v>
+        <v>0.8214488367694345</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>accz_energy</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.7753977260786415</v>
+        <v>0.8217966500640985</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>accz_iqr</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.7667160540529181</v>
+        <v>0.8233570813105521</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>accy_ptp</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.7689458420023958</v>
+        <v>0.8211535632473783</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.7673433789378559</v>
+        <v>0.8201836790450371</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>accx_energy</t>
+          <t>accy_max</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.7656515982598827</v>
+        <v>0.8226562007439632</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>accy_min</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.7748071790345292</v>
+        <v>0.8134207595149527</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>accy_entropy</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.7664838282579913</v>
+        <v>0.8134207595149527</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>accy_n_below_mean</t>
+          <t>accx_n_sign_changes</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.7696940083643318</v>
+        <v>0.8111699556564319</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>accz_min</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.7633314419015195</v>
+        <v>0.8102053254313515</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.7689248260933527</v>
+        <v>0.8038585209003215</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_5</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.7608704789525671</v>
+        <v>0.801322951474266</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.7589412185024063</v>
+        <v>0.8025776012441419</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>accy_svd_entropy</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.7547611541937247</v>
+        <v>0.7999842380682176</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>accx_sum</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.7517411680642246</v>
+        <v>0.8012546497698758</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.7594582098648677</v>
+        <v>0.7993201353424542</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.7620358111090095</v>
+        <v>0.8035317235147006</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>accx_entropy</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.7620358111090095</v>
+        <v>0.799351659206019</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.7620358111090095</v>
+        <v>0.803199672151819</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.755979026122775</v>
+        <v>0.8019187524956393</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.7505180421579135</v>
+        <v>0.8080228232772209</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_95</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.7585618813441775</v>
+        <v>0.8086659100939411</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>accz_lineintegral</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.7617825694050396</v>
+        <v>0.8103104049765673</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>accz_n_above_mean</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.7547296303301599</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_95</t>
+          <t>accx_svd_entropy</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.7227202992665448</v>
+        <v>0.7990301157976589</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr_5_95</t>
+          <t>accz_max</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.7218775613139146</v>
+        <v>0.7638547380366938</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.7186778891620957</v>
+        <v>0.7558634386230376</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.7206229115440388</v>
+        <v>0.75395519408192</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>accx_sum</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.7202961141584179</v>
+        <v>0.7763108673265662</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.7281339974360591</v>
+        <v>0.7654782170102767</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.7261994830086376</v>
+        <v>0.7658628081457663</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.7261994830086376</v>
+        <v>0.7665058949624866</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.7233318622197003</v>
+        <v>0.7536441586280815</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.7299518735682913</v>
+        <v>0.7446304352394764</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>accy_skewness</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.7309165037933716</v>
+        <v>0.7452997919425005</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>accx_n_above_mean</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.7325189668579114</v>
+        <v>0.7299129941365614</v>
       </c>
     </row>
     <row r="64">
@@ -1060,107 +1060,107 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.7325189668579114</v>
+        <v>0.7293014311834058</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_5</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.7419656179728054</v>
+        <v>0.7299392640228652</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>accx_perm_entropy</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.7521120988588361</v>
+        <v>0.7114957022466006</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>accy_iqr</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.7517853014732152</v>
+        <v>0.7211997982472732</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>accx_std</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.7435785889918669</v>
+        <v>0.7027562364710085</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>accx_skewness</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.7410062417249859</v>
+        <v>0.699846583863985</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>accz_iqr_5_95</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.741000987747725</v>
+        <v>0.7078694071412059</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>accz_rms</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.7406952062711473</v>
+        <v>0.7033572914696424</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>accz_lineintegral</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.7305161507260997</v>
+        <v>0.6853718765105185</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>accx_kurtosis</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.7285921442531997</v>
+        <v>0.6853718765105185</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>accx_max</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.7327722085618813</v>
+        <v>0.6879232078683564</v>
       </c>
     </row>
     <row r="75">
@@ -1170,167 +1170,167 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.7354128575331526</v>
+        <v>0.6787035285711284</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.727384780278671</v>
+        <v>0.6770800495975453</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.7228253788117605</v>
+        <v>0.6780289178908434</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>accz_pct_95</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.7224933274488787</v>
+        <v>0.6498108568186117</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>accz_pct_5</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.719468087342118</v>
+        <v>0.5805308618624299</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>accy_ptp</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.7030325956749259</v>
+        <v>0.5856808103734528</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>accz_svd_entropy</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.6949835025114012</v>
+        <v>0.5772366181199168</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.6822909442447933</v>
+        <v>0.5772366181199168</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>accz_n_sign_changes</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.6841413950360423</v>
+        <v>0.5840415694680874</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.68277641174369</v>
+        <v>0.5814376983376416</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>accz_n_below_mean</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.6776474791417102</v>
+        <v>0.5814376983376416</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>accy_n_above_mean</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.6740527078998801</v>
+        <v>0.5763507975537482</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>accz_sum</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.4849452535569426</v>
+        <v>0.5608746821343757</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>accz_kurtosis</t>
+          <t>accz_min</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.4852300191244773</v>
+        <v>0.5705052224533973</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>accy_min</t>
+          <t>accz_n_sign_changes</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.4823991761763655</v>
+        <v>0.5614074354286195</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.4915495029737512</v>
+        <v>0.5621293319042515</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>accx_lineintegral</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.4826093352667969</v>
+        <v>0.562894310993422</v>
       </c>
     </row>
     <row r="92">
@@ -1340,647 +1340,647 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.4914328646785616</v>
+        <v>0.5555145745329214</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.4917596620641825</v>
+        <v>0.5600266902044848</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr_5_95</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.4855767816236891</v>
+        <v>0.5600266902044848</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>accx_rms</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0.4798467940230755</v>
+        <v>0.5611752096336927</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>accy_mean</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.5079040833911271</v>
+        <v>0.5496049009099889</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>accy_perm_entropy</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.5091955110018284</v>
+        <v>0.5483555051173739</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>accy_iqr_5_95</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.4903557993401004</v>
+        <v>0.5297312065233382</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>accx_n_below_mean</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.4900290019544795</v>
+        <v>0.5274593867557741</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>accy_sum</t>
+          <t>accy_peaks</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.4945568795578253</v>
+        <v>0.5137916903095643</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.4929228926297207</v>
+        <v>0.5138284681503898</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr_5_95</t>
+          <t>accy_energy</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.492590841266839</v>
+        <v>0.5162946850766029</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>accz_peaks</t>
+          <t>accy_kurtosis</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0.4890958955929639</v>
+        <v>0.5207962927936448</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.5013817960195868</v>
+        <v>0.5169482798478447</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>accz_entropy</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0.5025208582897254</v>
+        <v>0.5054830506693567</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>accx_entropy</t>
+          <t>accy_n_below_mean</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.5025208582897254</v>
+        <v>0.5035012504465881</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>accx_std</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0.4986097976167959</v>
+        <v>0.4952367442153711</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.4973026080743123</v>
+        <v>0.4955425256919488</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>accz_skewness</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0.4996217136372234</v>
+        <v>0.4994851102284429</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0.4989681188659815</v>
+        <v>0.4928808608116344</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.5008973793161423</v>
+        <v>0.4922377739949141</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>accx_perm_entropy</t>
+          <t>accx_iqr_5_95</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0.496585965575941</v>
+        <v>0.4876521026416998</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>accz_n_below_mean</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.4952840300107181</v>
+        <v>0.4900657797953051</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>accy_mean</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.5025418741987685</v>
+        <v>0.4891011495702247</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_95</t>
+          <t>accy_std</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0.4992413256835425</v>
+        <v>0.4927904924027489</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t>accy_max</t>
+          <t>accy_lineintegral</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0.4887522854801085</v>
+        <v>0.4894857407057142</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.4887522854801085</v>
+        <v>0.4894857407057142</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>accz_entropy</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0.4887522854801085</v>
+        <v>0.487566988210075</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>accz_perm_entropy</t>
+          <t>accx_iqr</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.4736985898325032</v>
+        <v>0.4888636697980371</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>accy_svd_entropy</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0.4651020322384045</v>
+        <v>0.4855641720782632</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>accz_rms</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.4759966794863712</v>
+        <v>0.4882153290040561</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0.4806086207258895</v>
+        <v>0.4885368724124162</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>accy_n_sign_changes</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0.4806086207258895</v>
+        <v>0.4898125380913351</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0.4866286278712986</v>
+        <v>0.4898125380913351</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_5</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0.4976125927326986</v>
+        <v>0.4901445894542169</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>accy_n_above_mean</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0.4972963033015993</v>
+        <v>0.489517264569279</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>accx_n_sign_changes</t>
+          <t>accx_peaks</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.4979498980728412</v>
+        <v>0.4828131895845155</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>accy_rms</t>
+          <t>accy_sum</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0.4940703612634764</v>
+        <v>0.4730145219931488</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0.496031145577202</v>
+        <v>0.4802723661811992</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>accz_n_above_mean</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0.4976861484143497</v>
+        <v>0.480925960952441</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t>accx_skewness</t>
+          <t>accz_mean</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0.4976861484143497</v>
+        <v>0.4854632957148561</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0.4885148057079209</v>
+        <v>0.4814944412920581</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.4885148057079209</v>
+        <v>0.4637948426959208</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>accx_n_below_mean</t>
+          <t>accy_pct_95</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0.4898272492276654</v>
+        <v>0.4866654057121241</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>accx_kurtosis</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.4898272492276654</v>
+        <v>0.4892850387743521</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>accx_peaks</t>
+          <t>accx_pct_95</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.4924416283126327</v>
+        <v>0.4914938108147868</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>accy_n_sign_changes</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0.494054599331694</v>
+        <v>0.4928010003572704</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>accx_min</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.4880734716180148</v>
+        <v>0.4934598491057731</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>accz_sum</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>0.4861231952588109</v>
+        <v>0.4983397431855915</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0.4854853624193514</v>
+        <v>0.4986612865939516</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>accx_rms</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0.4912458230880776</v>
+        <v>0.4986823025029948</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>accx_n_above_mean</t>
+          <t>accx_energy</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0.4968381564844587</v>
+        <v>0.4993358972742366</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>accx_ptp</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>0.4968381564844587</v>
+        <v>0.4993358972742366</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>accy_perm_entropy</t>
+          <t>accy_pct_5</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>0.5025092995397517</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>accx_mean</t>
+          <t>accz_std</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>0.5001744320450581</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>0.5011916020427464</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>accz_energy</t>
+          <t>accx_ptp</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>0.5025092995397517</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>accz_kurtosis</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>0.5025092995397517</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>0.5025303154487948</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>accx_lineintegral</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>0.50057478511233</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>0.5005800390895908</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>0.4993201353424542</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>0.4976914023916105</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>accy_lineintegral</t>
+          <t>accx_max</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>0.4989985919340941</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>accz_std</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>0.4999894920454784</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>0.4999894920454784</v>
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>
